--- a/artfynd/A 19731-2024 artfynd.xlsx
+++ b/artfynd/A 19731-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129859998</v>
       </c>
       <c r="B2" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 19731-2024 artfynd.xlsx
+++ b/artfynd/A 19731-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129859998</v>
       </c>
       <c r="B2" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 19731-2024 artfynd.xlsx
+++ b/artfynd/A 19731-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129859998</v>
       </c>
       <c r="B2" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 19731-2024 artfynd.xlsx
+++ b/artfynd/A 19731-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129859998</v>
       </c>
       <c r="B2" t="n">
-        <v>57741</v>
+        <v>57899</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 19731-2024 artfynd.xlsx
+++ b/artfynd/A 19731-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129859998</v>
       </c>
       <c r="B2" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 19731-2024 artfynd.xlsx
+++ b/artfynd/A 19731-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129859998</v>
       </c>
       <c r="B2" t="n">
-        <v>57948</v>
+        <v>57975</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
